--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,49 +906,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104058676</v>
+        <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>80336</v>
+        <v>83343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster gällsjön, Mpd</t>
+          <t>Gällsjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546617</v>
+        <v>546642</v>
       </c>
       <c r="R4" t="n">
         <v>6916220</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +971,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +1001,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104058676</t>
+          <t>https://artportalen.se/Sighting/136776460</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104058672</v>
+        <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +1029,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster gällsjön, Mpd</t>
+          <t>Gällsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546617</v>
+        <v>546760</v>
       </c>
       <c r="R5" t="n">
-        <v>6916220</v>
+        <v>6916177</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1083,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,66 +1113,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104058672</t>
+          <t>https://artportalen.se/Sighting/136776456</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104058675</v>
+        <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>80467</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster gällsjön, Mpd</t>
+          <t>Gällsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546617</v>
+        <v>546926</v>
       </c>
       <c r="R6" t="n">
-        <v>6916220</v>
+        <v>6916251</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1195,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1225,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104058675</t>
+          <t>https://artportalen.se/Sighting/136776449</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104058683</v>
+        <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>79085</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,38 +1253,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Gällsjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546847</v>
+        <v>546786</v>
       </c>
       <c r="R7" t="n">
-        <v>6916192</v>
+        <v>6916164</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,22 +1307,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,18 +1337,1590 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136776455</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136776450</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>546867</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6916215</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776450</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136776454</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>546821</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6916145</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776454</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136776447</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79500</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>546952</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6916280</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776447</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136776453</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83463</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>546836</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6916178</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776453</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104058676</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>546617</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6916220</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104058676</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136776452</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>546856</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6916205</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776452</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136776461</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>546636</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6916212</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776461</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104058672</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>546617</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6916220</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104058672</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136776459</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>546650</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6916208</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776459</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136776451</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>546864</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6916212</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776451</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104058675</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>546617</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6916220</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104058675</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104058683</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>546847</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6916192</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/104058683</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136776457</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>546762</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6916173</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776457</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136776458</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gällsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>546758</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6916169</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136776458</t>
         </is>
       </c>
     </row>
@@ -1364,6 +2932,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136776460</v>
       </c>
       <c r="B4" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136776450</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136776454</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136776447</v>
       </c>
       <c r="B10" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136776453</v>
       </c>
       <c r="B11" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136776452</v>
       </c>
       <c r="B13" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136776461</v>
       </c>
       <c r="B14" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>136776459</v>
       </c>
       <c r="B16" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136776451</v>
       </c>
       <c r="B17" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136776457</v>
       </c>
       <c r="B20" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>136776458</v>
       </c>
       <c r="B21" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55176-2024 artfynd.xlsx
+++ b/artfynd/A 55176-2024 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>136776456</v>
       </c>
       <c r="B5" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136776449</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>136776455</v>
       </c>
       <c r="B7" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
